--- a/data/trans_orig/Q24D_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q24D_2-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de veces que han intentado dejar de fumar</t>
+          <t>Número medio de veces que han intentado dejar de fumar (tasa de respuesta: 91,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,64</t>
+          <t>1,52; 2,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,37</t>
+          <t>1,8; 2,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,94</t>
+          <t>2,04; 2,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,64</t>
+          <t>2,11; 3,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,65</t>
+          <t>1,8; 2,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,82</t>
+          <t>1,84; 2,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,13</t>
+          <t>1,52; 2,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,45</t>
+          <t>2,03; 4,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,51</t>
+          <t>1,8; 2,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,48</t>
+          <t>1,88; 2,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,48</t>
+          <t>1,86; 2,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,81</t>
+          <t>2,33; 3,91</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,41</t>
+          <t>1,91; 3,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,84</t>
+          <t>2,19; 2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 2,82</t>
+          <t>2,22; 2,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,88</t>
+          <t>2,0; 3,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 1,91</t>
+          <t>1,43; 1,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,73</t>
+          <t>2,17; 2,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,03</t>
+          <t>2,09; 3,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,97</t>
+          <t>2,26; 4,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,64</t>
+          <t>1,77; 2,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 2,7</t>
+          <t>2,23; 2,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 2,75</t>
+          <t>2,23; 2,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,96</t>
+          <t>2,36; 4,0</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 2,69</t>
+          <t>1,9; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,29</t>
+          <t>2,31; 4,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,4</t>
+          <t>2,34; 3,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,02</t>
+          <t>2,23; 4,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 2,81</t>
+          <t>2,23; 2,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 2,72</t>
+          <t>2,13; 2,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,19</t>
+          <t>2,39; 3,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,86</t>
+          <t>2,11; 2,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,63</t>
+          <t>2,14; 2,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,25</t>
+          <t>2,33; 3,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,06</t>
+          <t>2,43; 3,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,3</t>
+          <t>2,27; 3,27</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,79</t>
+          <t>2,56; 4,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,55</t>
+          <t>2,53; 3,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,67</t>
+          <t>2,03; 2,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,23</t>
+          <t>2,27; 3,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,28</t>
+          <t>2,02; 3,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,81</t>
+          <t>2,15; 2,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 2,95</t>
+          <t>2,23; 2,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,89</t>
+          <t>2,15; 2,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,07</t>
+          <t>2,49; 3,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,09</t>
+          <t>2,44; 3,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,65</t>
+          <t>2,18; 2,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 2,9</t>
+          <t>2,3; 2,89</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,24</t>
+          <t>2,31; 5,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,43</t>
+          <t>2,46; 3,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,85</t>
+          <t>2,29; 3,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,24</t>
+          <t>2,2; 7,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,26</t>
+          <t>1,51; 3,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,09</t>
+          <t>2,18; 6,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,89</t>
+          <t>1,84; 2,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,57</t>
+          <t>2,44; 3,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,62</t>
+          <t>2,35; 4,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,62</t>
+          <t>2,52; 3,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,21</t>
+          <t>2,18; 3,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,19</t>
+          <t>2,46; 4,86</t>
         </is>
       </c>
     </row>
@@ -1416,22 +1416,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,54</t>
+          <t>2,65; 4,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,76</t>
+          <t>2,09; 3,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,88</t>
+          <t>1,84; 2,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,25</t>
+          <t>2,62; 5,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,37 +1441,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,58</t>
+          <t>1,99; 4,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,56</t>
+          <t>1,73; 2,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,91</t>
+          <t>2,44; 4,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,15</t>
+          <t>2,48; 4,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,64</t>
+          <t>2,25; 3,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,69</t>
+          <t>1,93; 2,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,56</t>
+          <t>2,73; 4,6</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,44</t>
+          <t>2,72; 7,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,49</t>
+          <t>1,62; 3,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,31</t>
+          <t>2,33; 5,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,32</t>
+          <t>2,19; 6,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,97</t>
+          <t>2,46; 20,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,87</t>
+          <t>2,61; 6,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,67</t>
+          <t>1,76; 3,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,12</t>
+          <t>2,95; 10,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,54</t>
+          <t>2,7; 8,84</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,27</t>
+          <t>2,51; 3,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,05</t>
+          <t>2,52; 3,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 2,79</t>
+          <t>2,37; 2,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,77</t>
+          <t>2,56; 3,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,37</t>
+          <t>2,04; 2,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1726,32 +1726,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 2,75</t>
+          <t>2,29; 2,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,11</t>
+          <t>2,55; 3,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,82</t>
+          <t>2,33; 2,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,78</t>
+          <t>2,45; 2,77</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 2,68</t>
+          <t>2,38; 2,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,3</t>
+          <t>2,64; 3,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24D_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q24D_2-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>3,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>3,5</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,61</t>
+          <t>1,51; 2,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,35</t>
+          <t>1,77; 2,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,93</t>
+          <t>1,99; 3,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,51</t>
+          <t>2,08; 11,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,71</t>
+          <t>1,83; 2,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,87</t>
+          <t>1,83; 2,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,19</t>
+          <t>1,51; 2,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,54</t>
+          <t>2,37; 4,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,49</t>
+          <t>1,81; 2,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,49</t>
+          <t>1,86; 2,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,53</t>
+          <t>1,85; 2,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,91</t>
+          <t>2,49; 6,67</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>2,93</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,34</t>
+          <t>1,95; 3,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 2,82</t>
+          <t>2,18; 2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,82</t>
+          <t>2,23; 2,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,97</t>
+          <t>2,02; 3,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 1,87</t>
+          <t>1,42; 1,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,73</t>
+          <t>2,17; 2,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,09</t>
+          <t>2,09; 3,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,99</t>
+          <t>2,48; 4,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,61</t>
+          <t>1,79; 2,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,67</t>
+          <t>2,27; 2,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,74</t>
+          <t>2,24; 2,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,0</t>
+          <t>2,39; 3,99</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,64</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,7</t>
+          <t>1,91; 2,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,08</t>
+          <t>2,31; 3,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,31</t>
+          <t>2,34; 3,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,01</t>
+          <t>2,3; 3,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,8</t>
+          <t>2,23; 2,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,74</t>
+          <t>2,11; 2,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,13</t>
+          <t>2,36; 3,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 2,93</t>
+          <t>2,09; 2,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,62</t>
+          <t>2,14; 2,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,28</t>
+          <t>2,31; 3,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,1</t>
+          <t>2,46; 3,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,27</t>
+          <t>2,3; 3,17</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,76</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,86</t>
+          <t>2,6; 4,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,6</t>
+          <t>2,57; 3,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,67</t>
+          <t>2,01; 2,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,23</t>
+          <t>2,4; 4,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,8</t>
+          <t>2,16; 2,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,94</t>
+          <t>2,18; 2,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,92</t>
+          <t>2,19; 3,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,99</t>
+          <t>2,49; 3,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,07</t>
+          <t>2,47; 3,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,67</t>
+          <t>2,18; 2,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 2,89</t>
+          <t>2,4; 3,66</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>3,14</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,41</t>
+          <t>2,27; 5,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,42</t>
+          <t>2,45; 3,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,9</t>
+          <t>2,23; 3,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,84</t>
+          <t>2,38; 7,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,29</t>
+          <t>1,48; 3,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,33</t>
+          <t>2,14; 5,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,9</t>
+          <t>1,82; 2,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,58</t>
+          <t>2,42; 3,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,8</t>
+          <t>2,34; 4,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,69</t>
+          <t>2,52; 3,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,13</t>
+          <t>2,21; 3,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,86</t>
+          <t>2,52; 5,16</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,44</t>
         </is>
       </c>
     </row>
@@ -1416,22 +1416,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,55</t>
+          <t>2,63; 4,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,76</t>
+          <t>2,08; 3,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,94</t>
+          <t>1,82; 2,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,43</t>
+          <t>2,59; 5,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,37 +1441,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,64</t>
+          <t>2,0; 4,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,56</t>
+          <t>1,73; 2,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,97</t>
+          <t>2,42; 4,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,37</t>
+          <t>2,43; 4,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,66</t>
+          <t>2,24; 3,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,7</t>
+          <t>1,91; 2,68</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,6</t>
+          <t>2,75; 4,71</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,5</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,26</t>
+          <t>2,72; 7,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,62</t>
+          <t>1,54; 3,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,37</t>
+          <t>2,35; 5,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,42</t>
+          <t>2,1; 6,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 20,0</t>
+          <t>2,1; 16,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,97</t>
+          <t>2,33; 6,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,7</t>
+          <t>1,73; 3,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 10,63</t>
+          <t>2,96; 9,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,84</t>
+          <t>2,61; 9,3</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,25</t>
+          <t>2,51; 3,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,04</t>
+          <t>2,5; 3,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,76</t>
+          <t>2,38; 2,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,56; 3,71</t>
+          <t>2,74; 4,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,39</t>
+          <t>2,03; 2,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 2,63</t>
+          <t>2,29; 2,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 2,77</t>
+          <t>2,32; 2,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,14</t>
+          <t>2,56; 3,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 2,8</t>
+          <t>2,35; 2,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,77</t>
+          <t>2,44; 2,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 2,7</t>
+          <t>2,39; 2,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,29</t>
+          <t>2,75; 3,43</t>
         </is>
       </c>
     </row>
